--- a/02_DIA_inicio_2026_analisis_assets/rbd_9709_escuela-blue-star-college_nt1_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9709_escuela-blue-star-college_nt1_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53CCA43A-40CC-49C2-80C6-373BBFB6AEC6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82BDF702-34B6-4BE9-BA39-B66D7BD7D1DF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5AF81D3-FA6D-4CD1-8533-F9BB37CD1C35}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6D576FA-6FB0-410E-AE2D-08AE97F776FD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0CC1D7B-B594-40A3-8F6D-FB42FFA0A36A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61AD970D-8245-4CB6-B593-CB11F5C84B32}"/>
 </file>